--- a/public/excel/inventory/inventory.xlsx
+++ b/public/excel/inventory/inventory.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
   <si>
     <t xml:space="preserve">Tên Hàng</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">Đơn trọng</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bản mã 100 x 100 x 10</t>
   </si>
   <si>
@@ -44,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tấm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM220</t>
   </si>
   <si>
     <t xml:space="preserve">Tôn 11 sóng - 0.30 x 1080</t>
@@ -297,7 +303,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -320,6 +326,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -407,8 +417,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="45.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.36"/>
@@ -432,16 +442,19 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>1000</v>
@@ -449,16 +462,19 @@
       <c r="E2" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>1001</v>
@@ -466,16 +482,19 @@
       <c r="E3" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>1002</v>
@@ -483,16 +502,19 @@
       <c r="E4" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="F4" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>1003</v>
@@ -500,278 +522,335 @@
       <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="F5" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
+      <c r="A6" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1004</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>301.08</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1005</v>
       </c>
       <c r="E7" s="5"/>
+      <c r="F7" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>1006</v>
       </c>
       <c r="E8" s="5"/>
+      <c r="F8" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>1007</v>
       </c>
       <c r="E9" s="5"/>
+      <c r="F9" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>1008</v>
       </c>
       <c r="E10" s="5"/>
+      <c r="F10" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>1009</v>
       </c>
       <c r="E11" s="5"/>
+      <c r="F11" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>1010</v>
       </c>
       <c r="E12" s="5"/>
+      <c r="F12" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>1011</v>
       </c>
       <c r="E13" s="5"/>
+      <c r="F13" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>1012</v>
       </c>
       <c r="E14" s="5"/>
+      <c r="F14" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>1013</v>
       </c>
       <c r="E15" s="5"/>
+      <c r="F15" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1014</v>
       </c>
       <c r="E16" s="5"/>
+      <c r="F16" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>1015</v>
       </c>
       <c r="E17" s="5"/>
+      <c r="F17" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>1016</v>
       </c>
       <c r="E18" s="5"/>
+      <c r="F18" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1017</v>
       </c>
       <c r="E19" s="5"/>
+      <c r="F19" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>1018</v>
       </c>
       <c r="E20" s="5"/>
+      <c r="F20" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1019</v>
       </c>
       <c r="E21" s="5"/>
+      <c r="F21" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>1020</v>
       </c>
       <c r="E22" s="5"/>
+      <c r="F22" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1021</v>
       </c>
       <c r="E23" s="5"/>
+      <c r="F23" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
